--- a/ex01/ex01.xlsx
+++ b/ex01/ex01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anano\Desktop\Excel\Phase_1\ex00\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f2ee41b75427174/Desktop/excel/ex01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706E06E3-A46E-4CFE-A27F-6FB626D36CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{706E06E3-A46E-4CFE-A27F-6FB626D36CAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{2618DDF6-6538-4098-86D5-A1862A55BD2D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,17 +108,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2933"/>
-      <name val="Georgia"/>
-      <family val="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2933"/>
-      <name val="Georgia"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,32 +137,59 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -170,165 +207,38 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCFD6DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCFD6DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCFD6DD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCFD6DD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,227 +520,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="15.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>18500</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="4">
         <v>20100</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="4">
         <v>22300</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="4">
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>14200</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="4">
         <v>15750</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="4">
         <v>14980</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="4">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>8900</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>9150</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="4">
         <v>9780</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="4">
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>12100</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4">
         <v>11880</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="4">
         <v>13250</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="4">
         <v>520</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="4">
         <v>15600</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="4">
         <v>16220</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="4">
         <v>17010</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="4">
         <v>760</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="8">
         <f>SUM(B2:D2)</f>
         <v>60900</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <f>AVERAGE(B2:D2)</f>
         <v>20300</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="8">
         <f t="shared" ref="B11:B14" si="0">SUM(B3:D3)</f>
         <v>44930</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <f t="shared" ref="C11:C14" si="1">AVERAGE(B3:D3)</f>
         <v>14976.666666666666</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="8">
         <f t="shared" si="0"/>
         <v>27830</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <f t="shared" si="1"/>
         <v>9276.6666666666661</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="8">
         <f t="shared" si="0"/>
         <v>37230</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="9">
         <f t="shared" si="1"/>
         <v>12410</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="8">
         <f t="shared" si="0"/>
         <v>48830</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <f t="shared" si="1"/>
         <v>16276.666666666666</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="8">
         <f>SUM(B2:B6)</f>
         <v>69300</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="8">
         <f>SUM(C2:C6)</f>
         <v>73100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="8">
         <f>SUM(D2:D6)</f>
         <v>77320</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
       <c r="D21">
         <f>MAX(SUM(B2:B6),SUM(C2:C6),SUM(D2:D6))</f>
         <v>77320</v>
@@ -844,5 +754,6 @@
     <mergeCell ref="A21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>